--- a/docs/data/jp/xlsx/6836.xlsx
+++ b/docs/data/jp/xlsx/6836.xlsx
@@ -1909,7 +1909,7 @@
     <row r="7">
       <c r="A7" s="18" t="inlineStr">
         <is>
-          <t>Network Segment</t>
+          <t>네트워크 사업</t>
         </is>
       </c>
       <c r="B7" s="10" t="n"/>
@@ -2169,7 +2169,7 @@
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>Web3Segment</t>
+          <t>Web3 사업</t>
         </is>
       </c>
       <c r="B10" s="10" t="n"/>
@@ -9650,7 +9650,7 @@
     <row r="138">
       <c r="A138" s="18" t="inlineStr">
         <is>
-          <t>부문 · 외부 고객 매출</t>
+          <t>네트워크 사업 · 외부 고객 매출</t>
         </is>
       </c>
       <c r="L138" s="20" t="n">
@@ -9697,7 +9697,7 @@
     <row r="140">
       <c r="A140" s="18" t="inlineStr">
         <is>
-          <t>부문 · 외부 고객 매출</t>
+          <t>Web3 사업 · 외부 고객 매출</t>
         </is>
       </c>
       <c r="L140" s="20" t="n">
@@ -9857,7 +9857,7 @@
     <row r="147">
       <c r="A147" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 간 내부매출·대체</t>
+          <t>네트워크 사업 · 부문 간 내부매출·대체</t>
         </is>
       </c>
       <c r="L147" s="20" t="n">
@@ -9876,7 +9876,7 @@
     <row r="148">
       <c r="A148" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 간 내부매출·대체</t>
+          <t>Web3 사업 · 부문 간 내부매출·대체</t>
         </is>
       </c>
       <c r="L148" s="20" t="n">
@@ -9952,7 +9952,7 @@
     <row r="152">
       <c r="A152" s="18" t="inlineStr">
         <is>
-          <t>부문 · 계</t>
+          <t>네트워크 사업 · 계</t>
         </is>
       </c>
       <c r="L152" s="20" t="n">
@@ -9999,7 +9999,7 @@
     <row r="154">
       <c r="A154" s="18" t="inlineStr">
         <is>
-          <t>부문 · 계</t>
+          <t>Web3 사업 · 계</t>
         </is>
       </c>
       <c r="L154" s="20" t="n">
@@ -10159,7 +10159,7 @@
     <row r="161">
       <c r="A161" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 이익</t>
+          <t>네트워크 사업 · 부문 이익</t>
         </is>
       </c>
       <c r="L161" s="20" t="n">
@@ -10234,7 +10234,7 @@
     <row r="164">
       <c r="A164" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 이익</t>
+          <t>Web3 사업 · 부문 이익</t>
         </is>
       </c>
       <c r="L164" s="20" t="n">
@@ -11762,7 +11762,7 @@
     <row r="204">
       <c r="A204" s="18" t="inlineStr">
         <is>
-          <t>Proceeds From Investment In Securities Inv CF</t>
+          <t>투자사업조합 분배금 수입</t>
         </is>
       </c>
       <c r="O204" s="20" t="n">
